--- a/artfynd/A 32404-2024 artfynd.xlsx
+++ b/artfynd/A 32404-2024 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>119796603</v>
       </c>
       <c r="B6" t="n">
-        <v>105009</v>
+        <v>105032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>119820605</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
